--- a/artfynd/A 25348-2023 artfynd.xlsx
+++ b/artfynd/A 25348-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25348-2023 artfynd.xlsx
+++ b/artfynd/A 25348-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73268183</v>
+        <v>110250539</v>
       </c>
       <c r="B2" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövömosse, Vg</t>
+          <t>Lövö, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408648.8845055829</v>
+        <v>408662</v>
       </c>
       <c r="R2" t="n">
-        <v>6372471.11555678</v>
+        <v>6372761</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,12 +775,7 @@
         <v>73269134</v>
       </c>
       <c r="B3" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408739.2579005769</v>
+        <v>408739</v>
       </c>
       <c r="R3" t="n">
-        <v>6372561.038910827</v>
+        <v>6372561</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,19 +842,9 @@
           <t>2018-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,53 +872,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73269212</v>
+        <v>110250553</v>
       </c>
       <c r="B4" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövömosse, Vg</t>
+          <t>Lövö, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408609.1860219662</v>
+        <v>408831</v>
       </c>
       <c r="R4" t="n">
-        <v>6372646.762549306</v>
+        <v>6372750</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,22 +937,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +951,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1022,56 +969,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73269159</v>
+        <v>110260159</v>
       </c>
       <c r="B5" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövömosse, Vg</t>
+          <t>Stora Lövö, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408758.1324135197</v>
+        <v>408648</v>
       </c>
       <c r="R5" t="n">
-        <v>6372585.888296328</v>
+        <v>6372814</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,22 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,75 +1049,67 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73268351</v>
+        <v>110260179</v>
       </c>
       <c r="B6" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövömosse, Vg</t>
+          <t>Stora Lövö, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408743.8152453062</v>
+        <v>408693</v>
       </c>
       <c r="R6" t="n">
-        <v>6372548.031710327</v>
+        <v>6372862</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,22 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,77 +1147,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73269176</v>
+        <v>110260213</v>
       </c>
       <c r="B7" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövömosse, Vg</t>
+          <t>Stora Lövö, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408769.15493082</v>
+        <v>408740</v>
       </c>
       <c r="R7" t="n">
-        <v>6372596.93318221</v>
+        <v>6372811</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,22 +1231,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,34 +1245,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73269253</v>
+        <v>110250556</v>
       </c>
       <c r="B8" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,37 +1274,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lövömosse, Vg</t>
+          <t>Lövö, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408609.1860219662</v>
+        <v>408642</v>
       </c>
       <c r="R8" t="n">
-        <v>6372646.762549306</v>
+        <v>6372593</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1445,22 +1328,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1342,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1488,15 +1360,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73268349</v>
+        <v>110260023</v>
       </c>
       <c r="B9" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,40 +1371,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lövömosse, Vg</t>
+          <t>Stora Lövö, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408743.8152453062</v>
+        <v>408590</v>
       </c>
       <c r="R9" t="n">
-        <v>6372548.031710327</v>
+        <v>6372558</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,22 +1426,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ca 40 cm stor kudde</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,34 +1445,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73268216</v>
+        <v>73268183</v>
       </c>
       <c r="B10" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,36 +1474,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lövömosse, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408627.2601313739</v>
+        <v>408649</v>
       </c>
       <c r="R10" t="n">
-        <v>6372467.836613163</v>
+        <v>6372471</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1679,19 +1534,9 @@
           <t>2018-09-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,15 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110260252</v>
+        <v>73268351</v>
       </c>
       <c r="B11" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,38 +1575,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Lövö, Vg</t>
+          <t>Lövömosse, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408759.7784039739</v>
+        <v>408744</v>
       </c>
       <c r="R11" t="n">
-        <v>6372803.617032722</v>
+        <v>6372548</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,22 +1632,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,33 +1646,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110260139</v>
+        <v>73269159</v>
       </c>
       <c r="B12" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,38 +1676,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Lövö, Vg</t>
+          <t>Lövömosse, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408630.0469487356</v>
+        <v>408758</v>
       </c>
       <c r="R12" t="n">
-        <v>6372808.1389829</v>
+        <v>6372586</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1903,22 +1733,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,33 +1747,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110250547</v>
+        <v>73269212</v>
       </c>
       <c r="B13" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,34 +1777,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövö, Vg</t>
+          <t>Lövömosse, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408627.8227480174</v>
+        <v>408609</v>
       </c>
       <c r="R13" t="n">
-        <v>6372468.899437112</v>
+        <v>6372647</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2015,22 +1834,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,6 +1848,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2057,15 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110250546</v>
+        <v>73268349</v>
       </c>
       <c r="B14" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,34 +1878,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lövö, Vg</t>
+          <t>Lövömosse, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408653.7671630313</v>
+        <v>408744</v>
       </c>
       <c r="R14" t="n">
-        <v>6372472.619204144</v>
+        <v>6372548</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2127,22 +1935,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,6 +1949,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2169,15 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110250556</v>
+        <v>73269253</v>
       </c>
       <c r="B15" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,34 +1979,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lövö, Vg</t>
+          <t>Lövömosse, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408641.3899611316</v>
+        <v>408609</v>
       </c>
       <c r="R15" t="n">
-        <v>6372593.344992781</v>
+        <v>6372647</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2239,22 +2036,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,6 +2050,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2281,15 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110260100</v>
+        <v>110250542</v>
       </c>
       <c r="B16" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,38 +2080,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Lövö, Vg</t>
+          <t>Lövö, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408694.686272579</v>
+        <v>408730</v>
       </c>
       <c r="R16" t="n">
-        <v>6372735.714890142</v>
+        <v>6372507</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,93 +2137,78 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110260159</v>
+        <v>110250543</v>
       </c>
       <c r="B17" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Lövö, Vg</t>
+          <t>Lövö, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408649.03753328</v>
+        <v>408612</v>
       </c>
       <c r="R17" t="n">
-        <v>6372814.165047306</v>
+        <v>6372512</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2468,39 +2235,30 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2510,12 +2268,7 @@
         <v>110250544</v>
       </c>
       <c r="B18" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408646.8757499006</v>
+        <v>408647</v>
       </c>
       <c r="R18" t="n">
-        <v>6372837.871308147</v>
+        <v>6372838</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2580,19 +2333,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,15 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110260307</v>
+        <v>110260139</v>
       </c>
       <c r="B19" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,21 +2374,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2661,10 +2399,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408784.6371176154</v>
+        <v>408630</v>
       </c>
       <c r="R19" t="n">
-        <v>6372758.970236403</v>
+        <v>6372808</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2694,24 +2432,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>på flera träd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,12 +2464,7 @@
         <v>110260285</v>
       </c>
       <c r="B20" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,10 +2497,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408790.6925988569</v>
+        <v>408791</v>
       </c>
       <c r="R20" t="n">
-        <v>6372764.749119347</v>
+        <v>6372765</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2812,19 +2530,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,15 +2559,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110250541</v>
+        <v>110250540</v>
       </c>
       <c r="B21" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,10 +2594,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408622.1000945432</v>
+        <v>408762</v>
       </c>
       <c r="R21" t="n">
-        <v>6372453.971551376</v>
+        <v>6372542</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2924,19 +2627,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,15 +2656,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110250540</v>
+        <v>110250541</v>
       </c>
       <c r="B22" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408762.0154980309</v>
+        <v>408622</v>
       </c>
       <c r="R22" t="n">
-        <v>6372542.784496755</v>
+        <v>6372454</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3036,19 +2724,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,15 +2753,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110250543</v>
+        <v>110250557</v>
       </c>
       <c r="B23" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3091,21 +2764,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2590</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3115,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408612.6205548356</v>
+        <v>408633</v>
       </c>
       <c r="R23" t="n">
-        <v>6372511.720487995</v>
+        <v>6372435</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3148,28 +2821,17 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3188,15 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110250548</v>
+        <v>110259986</v>
       </c>
       <c r="B24" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,37 +2861,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lövö, Vg</t>
+          <t>Stora Lövö, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408654.4502251024</v>
+        <v>408740</v>
       </c>
       <c r="R24" t="n">
-        <v>6372839.31440892</v>
+        <v>6372556</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3261,19 +2919,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3288,27 +2936,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110250545</v>
+        <v>110260100</v>
       </c>
       <c r="B25" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3316,37 +2959,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lövö, Vg</t>
+          <t>Stora Lövö, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408794.4016352085</v>
+        <v>408695</v>
       </c>
       <c r="R25" t="n">
-        <v>6372761.977625173</v>
+        <v>6372736</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3373,19 +3017,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3400,66 +3034,62 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110259986</v>
+        <v>73268216</v>
       </c>
       <c r="B26" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Lövö, Vg</t>
+          <t>Lövömosse, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408739.6879928748</v>
+        <v>408627</v>
       </c>
       <c r="R26" t="n">
-        <v>6372556.189874476</v>
+        <v>6372468</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3483,22 +3113,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,33 +3127,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110260213</v>
+        <v>110250545</v>
       </c>
       <c r="B27" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3541,38 +3157,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stora Lövö, Vg</t>
+          <t>Lövö, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408739.9880546721</v>
+        <v>408795</v>
       </c>
       <c r="R27" t="n">
-        <v>6372809.974976939</v>
+        <v>6372762</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3599,19 +3214,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,49 +3231,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110250549</v>
+        <v>110250546</v>
       </c>
       <c r="B28" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3678,10 +3278,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408703.2601895195</v>
+        <v>408654</v>
       </c>
       <c r="R28" t="n">
-        <v>6372853.812287509</v>
+        <v>6372472</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3711,19 +3311,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3750,54 +3340,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110260023</v>
+        <v>110250547</v>
       </c>
       <c r="B29" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Lövö, Vg</t>
+          <t>Lövö, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408589.9643050849</v>
+        <v>408628</v>
       </c>
       <c r="R29" t="n">
-        <v>6372558.472460417</v>
+        <v>6372469</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3824,24 +3408,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ca 40 cm stor kudde</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3856,65 +3425,61 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110250554</v>
+        <v>110260064</v>
       </c>
       <c r="B30" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövö, Vg</t>
+          <t>Stora Lövö, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408627.8227480174</v>
+        <v>408603</v>
       </c>
       <c r="R30" t="n">
-        <v>6372468.899437112</v>
+        <v>6372676</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3941,19 +3506,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3968,65 +3523,61 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110250551</v>
+        <v>110260252</v>
       </c>
       <c r="B31" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövö, Vg</t>
+          <t>Stora Lövö, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408735.9057143632</v>
+        <v>408760</v>
       </c>
       <c r="R31" t="n">
-        <v>6372796.086821328</v>
+        <v>6372803</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4053,19 +3604,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4080,27 +3621,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110250539</v>
+        <v>110260307</v>
       </c>
       <c r="B32" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4108,37 +3644,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lövö, Vg</t>
+          <t>Stora Lövö, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408661.3175442665</v>
+        <v>408784</v>
       </c>
       <c r="R32" t="n">
-        <v>6372761.196801324</v>
+        <v>6372759</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4165,19 +3702,14 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>på flera träd</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4192,27 +3724,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110250557</v>
+        <v>92519867</v>
       </c>
       <c r="B33" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4220,37 +3747,49 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lövö, Vg</t>
+          <t>Moghult Lövö, Moghult, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408633.5251057465</v>
+        <v>408658</v>
       </c>
       <c r="R33" t="n">
-        <v>6372434.894782714</v>
+        <v>6372570</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4274,22 +3813,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>grop i sand vid rotvälta. Färsk kort spillning i gropen och bredvid.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4304,27 +3838,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Jens Ekdal</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Jens Ekdal</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>110250542</v>
+        <v>110250554</v>
       </c>
       <c r="B34" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4332,21 +3861,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4356,10 +3885,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408729.4375947864</v>
+        <v>408628</v>
       </c>
       <c r="R34" t="n">
-        <v>6372507.48757816</v>
+        <v>6372469</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4389,28 +3918,17 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4429,15 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>110260064</v>
+        <v>110250555</v>
       </c>
       <c r="B35" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,38 +3958,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stora Lövö, Vg</t>
+          <t>Lövö, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408602.3107786216</v>
+        <v>408670</v>
       </c>
       <c r="R35" t="n">
-        <v>6372676.490260483</v>
+        <v>6372876</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4503,19 +4015,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,66 +4032,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>110260179</v>
+        <v>73269176</v>
       </c>
       <c r="B36" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>102306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Lövö, Vg</t>
+          <t>Lövömosse, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>408693.1983746393</v>
+        <v>408769</v>
       </c>
       <c r="R36" t="n">
-        <v>6372861.565301945</v>
+        <v>6372597</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4613,22 +4114,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4637,55 +4128,51 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö, Stina Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>110250553</v>
+        <v>110250548</v>
       </c>
       <c r="B37" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4695,10 +4182,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>408830.7763084897</v>
+        <v>408655</v>
       </c>
       <c r="R37" t="n">
-        <v>6372750.409387585</v>
+        <v>6372839</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4728,19 +4215,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4764,6 +4241,200 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>110250549</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lövö, Vg</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>408703</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6372854</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mossebo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>110250551</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lövö, Vg</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>408736</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6372796</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mossebo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25348-2023 artfynd.xlsx
+++ b/artfynd/A 25348-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250539</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73269134</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250553</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260159</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260179</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260213</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1357,6 +1392,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250556</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260023</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73268183</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73268351</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73269159</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73269212</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73268349</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73269253</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2164,6 +2239,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250542</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2262,6 +2342,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250543</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2360,6 +2445,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250544</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2458,6 +2548,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260139</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2556,6 +2651,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260285</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2653,6 +2753,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250540</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2750,6 +2855,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250541</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2847,6 +2957,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250557</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2945,6 +3060,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259986</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3043,6 +3163,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260100</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3143,6 +3268,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73268216</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3240,6 +3370,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250545</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3337,6 +3472,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250546</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3434,6 +3574,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250547</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3532,6 +3677,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260064</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3630,6 +3780,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260252</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3733,6 +3888,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260307</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3847,6 +4007,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92519867</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3944,6 +4109,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250554</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4041,6 +4211,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250555</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4144,6 +4319,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73269176</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4241,6 +4421,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250548</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4338,6 +4523,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250549</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4435,8 +4625,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110250551</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>